--- a/docs/Test_Case_Matrix.xlsx
+++ b/docs/Test_Case_Matrix.xlsx
@@ -1361,7 +1361,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:M46"/>
+  <dimension ref="A1:M47"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="9"/>
@@ -1447,10 +1447,26 @@
       <c r="I2" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="J2" s="3"/>
-      <c r="K2" s="6"/>
-      <c r="L2" s="3"/>
-      <c r="M2" s="3"/>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>First-Time Setup was displayed instead of the Main Page.</t>
+        </is>
+      </c>
+      <c r="K2" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>Project owner</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
@@ -1480,10 +1496,26 @@
       <c r="I3" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="J3" s="3"/>
-      <c r="K3" s="6"/>
-      <c r="L3" s="3"/>
-      <c r="M3" s="3"/>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>Both halves confirmed. Closing setup without Get Started left no database and re-showed setup on the next launch. After completing setup, the following launch opened directly on the Main Page.</t>
+        </is>
+      </c>
+      <c r="K3" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>Project owner</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
@@ -1492,11 +1524,15 @@
       <c r="B4" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C4" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>29</v>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Letters cannot be entered into the Slip Length field</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>NT / EP</t>
+        </is>
       </c>
       <c r="E4" s="7" t="s">
         <v>30</v>
@@ -1504,19 +1540,42 @@
       <c r="F4" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="G4" s="3" t="s">
-        <v>32</v>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>1. Set Paper Size to Small240x102 so the Slip Length field appears
+2. Attempt to type 'abc' into Slip Length
+3. Type a valid value such as 5.5
+4. Attempt to type a second decimal separator</t>
+        </is>
       </c>
       <c r="H4" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="I4" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="J4" s="3"/>
-      <c r="K4" s="6"/>
-      <c r="L4" s="3"/>
-      <c r="M4" s="3"/>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>Letters produce no input at all. A valid decimal is accepted and a second separator is refused. A blank or pasted value is still caught by the Get Started validation as a backstop.</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>Typing 'abc' produced no input. '5.5' was accepted and a second decimal separator was refused. Re-tested after the DEF-029 fix.</t>
+        </is>
+      </c>
+      <c r="K4" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>Project owner</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
@@ -1554,10 +1613,26 @@
           <t>A 'Default' preset exists and is active, AND it carries the printer, paper size and slip length chosen during setup -- not the seeded fallback values. Existence alone is not sufficient: see TC-044, which covers the paper-size case explicitly.</t>
         </is>
       </c>
-      <c r="J5" s="3"/>
-      <c r="K5" s="6"/>
-      <c r="L5" s="3"/>
-      <c r="M5" s="3"/>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>A4 selected with the preset box unticked. Printer Settings showed Preset = Default and Paper Profile Size = A4. The database holds exactly one profile, named Default, mode A4, 210 x 297 mm, IsActive = 1.</t>
+        </is>
+      </c>
+      <c r="K5" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>Project owner</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
@@ -2989,10 +3064,26 @@
           <t>The active preset uses the paper size chosen during setup (A4 = 210 x 297 mm). The checkbox decides which profile receives the values, never whether they are kept.</t>
         </is>
       </c>
-      <c r="J45" s="3"/>
-      <c r="K45" s="6"/>
-      <c r="L45" s="3"/>
-      <c r="M45" s="3"/>
+      <c r="J45" s="3" t="inlineStr">
+        <is>
+          <t>Same run as TC-004. The active profile carried the chosen A4 size (210 x 297 mm) rather than the seeded Small240x102 fallback.</t>
+        </is>
+      </c>
+      <c r="K45" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L45" s="3" t="inlineStr">
+        <is>
+          <t>Project owner</t>
+        </is>
+      </c>
+      <c r="M45" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
     </row>
     <row r="46" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="2" t="inlineStr">
@@ -3047,6 +3138,76 @@
       <c r="K46" s="6"/>
       <c r="L46" s="3"/>
       <c r="M46" s="3"/>
+    </row>
+    <row r="47" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>TC-046</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>First-Time Setup</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>Abandoning setup leaves no database and setup reappears</t>
+        </is>
+      </c>
+      <c r="D47" s="4" t="inlineStr">
+        <is>
+          <t>FT / NT</t>
+        </is>
+      </c>
+      <c r="E47" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F47" s="3" t="inlineStr">
+        <is>
+          <t>No WeighbridgeData.db exists in the application folder</t>
+        </is>
+      </c>
+      <c r="G47" s="3" t="inlineStr">
+        <is>
+          <t>1. Launch the application so First-Time Setup appears
+2. Click 'Customize Fields...' and close that window
+3. Close the setup screen with the X, WITHOUT clicking Get Started
+4. Relaunch the application</t>
+        </is>
+      </c>
+      <c r="H47" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I47" s="3" t="inlineStr">
+        <is>
+          <t>No database is left behind and First-Time Setup appears again. Only Get Started commits a setup; abandoning it must never leave a half-configured system that skips setup on later launches.</t>
+        </is>
+      </c>
+      <c r="J47" s="3" t="inlineStr">
+        <is>
+          <t>Setup appeared again on relaunch. The database created by Customize Fields was removed when the screen was closed.</t>
+        </is>
+      </c>
+      <c r="K47" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L47" s="3" t="inlineStr">
+        <is>
+          <t>Project owner</t>
+        </is>
+      </c>
+      <c r="M47" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/docs/Test_Case_Matrix.xlsx
+++ b/docs/Test_Case_Matrix.xlsx
@@ -1662,10 +1662,26 @@
       <c r="I6" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="J6" s="3"/>
-      <c r="K6" s="6"/>
-      <c r="L6" s="3"/>
-      <c r="M6" s="3"/>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>Save was blocked with a Validation message reading 'Truck Reg (Field 1) is required before saving.' SlipID remained 'Auto-assigned' and the database row count was unchanged, confirming nothing was written. The Bill Number generated for the abandoned form was discarded rather than consumed, so no gap was created in the sequence.</t>
+        </is>
+      </c>
+      <c r="K6" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>Project owner</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
@@ -1695,10 +1711,26 @@
       <c r="I7" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="J7" s="3"/>
-      <c r="K7" s="6"/>
-      <c r="L7" s="3"/>
-      <c r="M7" s="3"/>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>With Truck Reg cleared on an existing saved draft, Print was blocked with 'Truck Reg (Field 1) is required before printing.' - the same strictness applied to Tons.</t>
+        </is>
+      </c>
+      <c r="K7" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>Project owner</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
@@ -1728,10 +1760,26 @@
       <c r="I8" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="J8" s="3"/>
-      <c r="K8" s="6"/>
-      <c r="L8" s="3"/>
-      <c r="M8" s="3"/>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>The slip saved as an Unprinted draft with Tons left blank, and the Main Page tile appeared showing Tons: 0.</t>
+        </is>
+      </c>
+      <c r="K8" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>Project owner</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
@@ -1761,10 +1809,26 @@
       <c r="I9" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="J9" s="3"/>
-      <c r="K9" s="6"/>
-      <c r="L9" s="3"/>
-      <c r="M9" s="3"/>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>Print on the draft with Tons still blank was blocked with 'Tons must be filled in before printing.'</t>
+        </is>
+      </c>
+      <c r="K9" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>Project owner</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
@@ -1794,10 +1858,26 @@
       <c r="I10" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="J10" s="3"/>
-      <c r="K10" s="6"/>
-      <c r="L10" s="3"/>
-      <c r="M10" s="3"/>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>Tons entered as 36,22 using a comma was stored in the database as 36.22 with a period.</t>
+        </is>
+      </c>
+      <c r="K10" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>Project owner</t>
+        </is>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
@@ -1827,10 +1907,26 @@
       <c r="I11" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="J11" s="3"/>
-      <c r="K11" s="6"/>
-      <c r="L11" s="3"/>
-      <c r="M11" s="3"/>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>A second decimal separator could not be typed at all - attempting 15.5.3 was refused at the keystroke, so the invalid value never reached the field.</t>
+        </is>
+      </c>
+      <c r="K11" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>Project owner</t>
+        </is>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
@@ -1860,10 +1956,26 @@
       <c r="I12" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="J12" s="3"/>
-      <c r="K12" s="6"/>
-      <c r="L12" s="3"/>
-      <c r="M12" s="3"/>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>Re-opening the draft from its tile showed SlipID 1 and Bill Number 20260808-103823, identical to the values before the edit and re-save. No new identifiers were allocated.</t>
+        </is>
+      </c>
+      <c r="K12" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>Project owner</t>
+        </is>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
@@ -1992,10 +2104,26 @@
       <c r="I16" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="J16" s="3"/>
-      <c r="K16" s="6"/>
-      <c r="L16" s="3"/>
-      <c r="M16" s="3"/>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>Saving a new slip with Truck Reg LFN550NW produced a Main Page tile showing the registration, SlipID and Tons.</t>
+        </is>
+      </c>
+      <c r="K16" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t>Project owner</t>
+        </is>
+      </c>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
     </row>
     <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="2" t="s">

--- a/docs/Test_Case_Matrix.xlsx
+++ b/docs/Test_Case_Matrix.xlsx
@@ -2153,10 +2153,26 @@
       <c r="I17" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="J17" s="3"/>
-      <c r="K17" s="6"/>
-      <c r="L17" s="3"/>
-      <c r="M17" s="3"/>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>Clicking Print opened the Print Preview before anything reached the printer. No paper was committed until Print was pressed on the preview itself.</t>
+        </is>
+      </c>
+      <c r="K17" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t>Project owner</t>
+        </is>
+      </c>
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
     </row>
     <row r="18" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="2" t="s">
@@ -2186,10 +2202,26 @@
       <c r="I18" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="J18" s="3"/>
-      <c r="K18" s="6"/>
-      <c r="L18" s="3"/>
-      <c r="M18" s="3"/>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>Confirming the print set slip 1 to Printed with PrintedAt 2026-08-08 11:13:58, removed its Main Page tile, and the slip appeared in Slip History. The daily summary updated to Loads: 1, Total Tons: 36.220 t.</t>
+        </is>
+      </c>
+      <c r="K18" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t>Project owner</t>
+        </is>
+      </c>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
     </row>
     <row r="19" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="2" t="s">
@@ -2228,10 +2260,26 @@
           <t>The operator is returned to the same Print Preview, re-rendered with the new settings, rather than being sent to the printer or back to the Main Page.</t>
         </is>
       </c>
-      <c r="J19" s="3"/>
-      <c r="K19" s="6"/>
-      <c r="L19" s="3"/>
-      <c r="M19" s="3"/>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>Opened Calibrate Print from the preview, changed the font scale from 2.35 to 2.55 and saved. The operator was returned to the same Print Preview, re-rendered with the new scale, rather than being sent onward.</t>
+        </is>
+      </c>
+      <c r="K19" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L19" s="3" t="inlineStr">
+        <is>
+          <t>Project owner</t>
+        </is>
+      </c>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
     </row>
     <row r="20" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="2" t="s">
@@ -2261,10 +2309,26 @@
       <c r="I20" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="J20" s="3"/>
-      <c r="K20" s="6"/>
-      <c r="L20" s="3"/>
-      <c r="M20" s="3"/>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>Cancel on a saved draft offered Void / Close / Cancel. Confirming with a blank reason was refused with 'A void reason is required.' and the dialog stayed open. After entering a reason the slip voided, its tile disappeared, and it appeared in the Voided view with VoidedAt 2026-08-08 11:25:06.</t>
+        </is>
+      </c>
+      <c r="K20" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L20" s="3" t="inlineStr">
+        <is>
+          <t>Project owner</t>
+        </is>
+      </c>
+      <c r="M20" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
     </row>
     <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="2" t="s">
@@ -2294,10 +2358,26 @@
       <c r="I21" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="J21" s="3"/>
-      <c r="K21" s="6"/>
-      <c r="L21" s="3"/>
-      <c r="M21" s="3"/>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>The reason field stopped accepting input at exactly 20 characters. Confirmed on both void dialogs - the one reached from Cancel on a draft, and the one reached from Void Slip on a printed slip. Stored values measured 20 and 6 characters.</t>
+        </is>
+      </c>
+      <c r="K21" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t>Project owner</t>
+        </is>
+      </c>
+      <c r="M21" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
     </row>
     <row r="22" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="2" t="s">
@@ -2327,10 +2407,26 @@
       <c r="I22" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="J22" s="3"/>
-      <c r="K22" s="6"/>
-      <c r="L22" s="3"/>
-      <c r="M22" s="3"/>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>Slip 1, already Printed, was voided from Slip History with a reason. A blank reason was refused first. The slip moved to Voided with VoidedAt 2026-08-08 11:33:20 while PrintedAt was preserved at 11:13:58, so the record still shows both that it was printed and when it was voided. Nothing was deleted.</t>
+        </is>
+      </c>
+      <c r="K22" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
+          <t>Project owner</t>
+        </is>
+      </c>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
     </row>
     <row r="23" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="2" t="s">
@@ -2360,10 +2456,26 @@
       <c r="I23" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="J23" s="3"/>
-      <c r="K23" s="6"/>
-      <c r="L23" s="3"/>
-      <c r="M23" s="3"/>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>Slip 1 was reprinted twice from Slip History, at 11:18 and 11:20, with no restriction, warning or error on either attempt.</t>
+        </is>
+      </c>
+      <c r="K23" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L23" s="3" t="inlineStr">
+        <is>
+          <t>Project owner</t>
+        </is>
+      </c>
+      <c r="M23" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
     </row>
     <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="2" t="s">
@@ -2723,10 +2835,26 @@
       <c r="I34" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="J34" s="3"/>
-      <c r="K34" s="6"/>
-      <c r="L34" s="3"/>
-      <c r="M34" s="3"/>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>The Printed view showed only Printed slips and the Voided view only Voided ones. The Voided view additionally showed the Void Reason and Voided At columns, both populated, and those columns were absent from the Printed view.</t>
+        </is>
+      </c>
+      <c r="K34" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L34" s="3" t="inlineStr">
+        <is>
+          <t>Project owner</t>
+        </is>
+      </c>
+      <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
     </row>
     <row r="35" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="2" t="s">
@@ -2876,10 +3004,26 @@
       <c r="I38" s="3" t="s">
         <v>225</v>
       </c>
-      <c r="J38" s="3"/>
-      <c r="K38" s="6"/>
-      <c r="L38" s="3"/>
-      <c r="M38" s="3"/>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>With the only slip printed and its tile removed, the Main Page showed 'Welcome! Your slips will appear here. Click New Slip to get started.' instead of an empty panel.</t>
+        </is>
+      </c>
+      <c r="K38" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L38" s="3" t="inlineStr">
+        <is>
+          <t>Project owner</t>
+        </is>
+      </c>
+      <c r="M38" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
     </row>
     <row r="39" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="2" t="s">
@@ -3030,10 +3174,26 @@
           <t>The edited values are written to the database before printing, so the printed slip and its stored row are identical. No printed slip may ever disagree with its database record.</t>
         </is>
       </c>
-      <c r="J42" s="3"/>
-      <c r="K42" s="6"/>
-      <c r="L42" s="3"/>
-      <c r="M42" s="3"/>
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t>Rom Type and Tons were edited on a saved draft and Print was clicked without Save. The database row held the edited values (MG2/3W and 36.22) while still Unprinted, proving the edits were persisted at Print time; the preview and the printed slip carried the same values, and Slip History confirmed them after the print completed.</t>
+        </is>
+      </c>
+      <c r="K42" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L42" s="3" t="inlineStr">
+        <is>
+          <t>Project owner</t>
+        </is>
+      </c>
+      <c r="M42" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
     </row>
     <row r="43" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="2" t="inlineStr">
@@ -3084,10 +3244,26 @@
           <t>The preview shows the slip's ORIGINAL print date, not today's. Printed At is unchanged afterwards and the slip holds its position in the history ordering.</t>
         </is>
       </c>
-      <c r="J43" s="3"/>
-      <c r="K43" s="6"/>
-      <c r="L43" s="3"/>
-      <c r="M43" s="3"/>
+      <c r="J43" s="3" t="inlineStr">
+        <is>
+          <t>Slip 1 was reprinted twice at 11:18 and 11:20. Both previews showed 'Printed: 2026-08-08 11:13' - the original print time, not the time of the reprint - and PrintedAt in the database remained 11:13:58 throughout, so the slip kept its position in the history ordering.</t>
+        </is>
+      </c>
+      <c r="K43" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L43" s="3" t="inlineStr">
+        <is>
+          <t>Project owner</t>
+        </is>
+      </c>
+      <c r="M43" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
     </row>
     <row r="44" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="2" t="inlineStr">
@@ -3137,10 +3313,26 @@
           <t>All four agree with the PC clock. None is offset by the machine's UTC difference. The same holds on any machine the application is installed on.</t>
         </is>
       </c>
-      <c r="J44" s="3"/>
-      <c r="K44" s="6"/>
-      <c r="L44" s="3"/>
-      <c r="M44" s="3"/>
+      <c r="J44" s="3" t="inlineStr">
+        <is>
+          <t>All four sources agreed with the PC clock, with no UTC offset. Slip 1: Bill Number 20260808-103823 (10:38:23), CreatedAt 10:41:10, PrintedAt 11:13:58, and the date printed on the slip read 2026-08-08 11:13. The same held for slips 2 and 3.</t>
+        </is>
+      </c>
+      <c r="K44" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L44" s="3" t="inlineStr">
+        <is>
+          <t>Project owner</t>
+        </is>
+      </c>
+      <c r="M44" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
     </row>
     <row r="45" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="2" t="inlineStr">

--- a/docs/Test_Case_Matrix.xlsx
+++ b/docs/Test_Case_Matrix.xlsx
@@ -2505,10 +2505,26 @@
       <c r="I24" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="J24" s="3"/>
-      <c r="K24" s="6"/>
-      <c r="L24" s="3"/>
-      <c r="M24" s="3"/>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>Typing into a Label Name cell stopped at exactly 14 characters; a longer label could not be entered at all.</t>
+        </is>
+      </c>
+      <c r="K24" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
+          <t>Project owner</t>
+        </is>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
     </row>
     <row r="25" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="2" t="s">
@@ -2538,10 +2554,26 @@
       <c r="I25" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="J25" s="3"/>
-      <c r="K25" s="6"/>
-      <c r="L25" s="3"/>
-      <c r="M25" s="3"/>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>Field1 (Truck Reg) and Field7 (Tons) were greyed out and could not be clicked in the 'fields that print' list on the Slip Design tab, with the explanatory note shown beneath the list.</t>
+        </is>
+      </c>
+      <c r="K25" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L25" s="3" t="inlineStr">
+        <is>
+          <t>Project owner</t>
+        </is>
+      </c>
+      <c r="M25" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
     </row>
     <row r="26" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="2" t="s">
@@ -2571,10 +2603,26 @@
       <c r="I26" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="J26" s="3"/>
-      <c r="K26" s="6"/>
-      <c r="L26" s="3"/>
-      <c r="M26" s="3"/>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>Field1 and Field7 were likewise greyed out and unclickable in the 'required before printing' list, and remained checked.</t>
+        </is>
+      </c>
+      <c r="K26" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L26" s="3" t="inlineStr">
+        <is>
+          <t>Project owner</t>
+        </is>
+      </c>
+      <c r="M26" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
     </row>
     <row r="27" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="2" t="s">

--- a/docs/Test_Case_Matrix.xlsx
+++ b/docs/Test_Case_Matrix.xlsx
@@ -2652,10 +2652,26 @@
       <c r="I27" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="J27" s="3"/>
-      <c r="K27" s="6"/>
-      <c r="L27" s="3"/>
-      <c r="M27" s="3"/>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>Field6 was renamed from 'Destination' to 'Slot number' and Field9 from 'Slot' to 'Destination'. Both new labels appeared in all three required places: the Create Slip data entry form, the Slip History grid headers, and the exported spreadsheet's column headers. Field10 was cleared and then restored to 'Client', which also propagated.</t>
+        </is>
+      </c>
+      <c r="K27" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L27" s="3" t="inlineStr">
+        <is>
+          <t>Project owner</t>
+        </is>
+      </c>
+      <c r="M27" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
     </row>
     <row r="28" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="2" t="s">
@@ -2932,10 +2948,26 @@
       <c r="I35" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="J35" s="3"/>
-      <c r="K35" s="6"/>
-      <c r="L35" s="3"/>
-      <c r="M35" s="3"/>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t>Export headers carried the current Customize Slips labels, not generic field names: 'Slot number' for Field6, 'Destination' for Field9 and 'Client' for Field10. While Field10's label was temporarily blank, the header fell back to 'Field 10' as designed, spec section 4.4 permitting blank labels.</t>
+        </is>
+      </c>
+      <c r="K35" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L35" s="3" t="inlineStr">
+        <is>
+          <t>Project owner</t>
+        </is>
+      </c>
+      <c r="M35" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
     </row>
     <row r="36" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="2" t="s">
@@ -2978,10 +3010,26 @@
           <t>The hidden field's column is still present under its current label and its cells are blank. Every export has the same 17-column structure regardless of which fields are hidden, so exported files stay comparable to one another over time.</t>
         </is>
       </c>
-      <c r="J36" s="3"/>
-      <c r="K36" s="6"/>
-      <c r="L36" s="3"/>
-      <c r="M36" s="3"/>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>Field9 held PO9/7 on all three slips before being hidden. After hiding it, column N of the export was still headed 'Destination' but contained no value in any data row - verified at the XML level, where no cell element is written for that column while every other populated column is present. The column structure stayed identical between the Printed and Voided exports at 17 columns each, so the two files remain directly comparable.</t>
+        </is>
+      </c>
+      <c r="K36" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L36" s="3" t="inlineStr">
+        <is>
+          <t>Project owner</t>
+        </is>
+      </c>
+      <c r="M36" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
     </row>
     <row r="37" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="2" t="s">
@@ -3019,10 +3067,26 @@
           <t>The exported file includes Void Reason populated with each slip's recorded reason, and Voided At showing when the void happened.</t>
         </is>
       </c>
-      <c r="J37" s="3"/>
-      <c r="K37" s="6"/>
-      <c r="L37" s="3"/>
-      <c r="M37" s="3"/>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t>The Voided export included both audit columns populated: Voided At showed 2026-08-08 11:33:20 and 11:25:06, and Void Reason showed 'Reason12345698775222' and 'reason'. Slip 1 additionally retained its Printed At of 2026-08-08 11:13:58 despite being voided, so the exported record shows both that it was printed and when it was voided.</t>
+        </is>
+      </c>
+      <c r="K37" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L37" s="3" t="inlineStr">
+        <is>
+          <t>Project owner</t>
+        </is>
+      </c>
+      <c r="M37" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
     </row>
     <row r="38" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="2" t="s">
@@ -3502,10 +3566,26 @@
           <t>Printed slips filter on Printed At, voided slips on Voided At and drafts on Created At. A slip printed inside the range appears regardless of when it was created.</t>
         </is>
       </c>
-      <c r="J46" s="3"/>
-      <c r="K46" s="6"/>
-      <c r="L46" s="3"/>
-      <c r="M46" s="3"/>
+      <c r="J46" s="3" t="inlineStr">
+        <is>
+          <t>Slip 3 was created 2026-08-08 11:30:06 and printed 2026-08-10 11:26:33, two days apart. Filtering the Printed view to 10 August returned the slip; filtering to 8 August returned nothing (Total Slips: 0). Under the previous CreatedAt-based filter the result would have been exactly inverted, confirming the DEF-024 fix.</t>
+        </is>
+      </c>
+      <c r="K46" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L46" s="3" t="inlineStr">
+        <is>
+          <t>Project owner</t>
+        </is>
+      </c>
+      <c r="M46" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
     </row>
     <row r="47" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="2" t="inlineStr">

--- a/docs/Test_Case_Matrix.xlsx
+++ b/docs/Test_Case_Matrix.xlsx
@@ -2005,10 +2005,26 @@
       <c r="I13" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="J13" s="3"/>
-      <c r="K13" s="6"/>
-      <c r="L13" s="3"/>
-      <c r="M13" s="3"/>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>On the Slip History Edit tab the Slip ID showed 3 in a greyed, uneditable box. On Create Slip the field read 'Auto-assigned' before saving and 4 afterwards, read-only in both states. A printed slip cannot be opened in Create Slip at all - editing a printed slip is done through the History Edit tab by design - so there is no screen anywhere that exposes SlipID as editable.</t>
+        </is>
+      </c>
+      <c r="K13" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t>Project owner</t>
+        </is>
+      </c>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
@@ -2038,10 +2054,26 @@
       <c r="I14" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="J14" s="3"/>
-      <c r="K14" s="6"/>
-      <c r="L14" s="3"/>
-      <c r="M14" s="3"/>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>Bill Number is absent from the Slip History Edit tab entirely, so there is no control through which to change it. On Create Slip it is displayed read-only. The database additionally rejects any UPDATE to the column through the PreventBillNumberChange trigger, giving protection at both the UI and storage layers.</t>
+        </is>
+      </c>
+      <c r="K14" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t>Project owner</t>
+        </is>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
     </row>
     <row r="15" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="s">
@@ -2071,10 +2103,26 @@
       <c r="I15" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="J15" s="3"/>
-      <c r="K15" s="6"/>
-      <c r="L15" s="3"/>
-      <c r="M15" s="3"/>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>Slip 4 was created with Bill Number 20260811-082225 and then voided at 08:24:24 with reason 'Test'. The next new slip opened with Bill Number 20260811-082426 - a different and later value. The voided slip retained its own number and it was never reissued.</t>
+        </is>
+      </c>
+      <c r="K15" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t>Project owner</t>
+        </is>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
     </row>
     <row r="16" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="2" t="s">
@@ -2833,10 +2881,26 @@
       <c r="I32" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="J32" s="3"/>
-      <c r="K32" s="6"/>
-      <c r="L32" s="3"/>
-      <c r="M32" s="3"/>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>Selecting slip 3 in the grid populated the Edit Slip tab with that slip's details: Slip ID 3, Truck Reg LFN550NW, Stockpile Name MSMG2/3W, Rom Type MG2/3W, Block Nr BL7, Size -40, Slot number ACACIA and Tons 36.98. Every field was editable except Slip ID, and Bill Number was not present.</t>
+        </is>
+      </c>
+      <c r="K32" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L32" s="3" t="inlineStr">
+        <is>
+          <t>Project owner</t>
+        </is>
+      </c>
+      <c r="M32" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
     </row>
     <row r="33" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="2" t="s">

--- a/docs/Test_Case_Matrix.xlsx
+++ b/docs/Test_Case_Matrix.xlsx
@@ -2749,10 +2749,26 @@
       <c r="I28" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="J28" s="3"/>
-      <c r="K28" s="6"/>
-      <c r="L28" s="3"/>
-      <c r="M28" s="3"/>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>A second preset named 'TC-27 test' was created with paper Small151x151 and 2 copies, alongside the existing 'Default' at A4 with 1 copy. Switching the dropdown between them changed the form values to match each preset, and the selection also became the active profile in the database: TC-27 test IsActive=1, Default IsActive=0. GlobalSettings synced to the active preset's paper size and copy count.</t>
+        </is>
+      </c>
+      <c r="K28" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L28" s="3" t="inlineStr">
+        <is>
+          <t>Project owner</t>
+        </is>
+      </c>
+      <c r="M28" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
     </row>
     <row r="29" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="2" t="s">
@@ -2782,10 +2798,26 @@
       <c r="I29" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="J29" s="3"/>
-      <c r="K29" s="6"/>
-      <c r="L29" s="3"/>
-      <c r="M29" s="3"/>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>Calibration and configuration were saved to 'TC-27 test' several times, including a font scale change from 2.60 to 1.60. The database afterwards held exactly two profiles, Default and TC-27 test, with no duplicate entry, and TC-27 test carried the latest values. This confirms the ON CONFLICT(ProfileName) DO UPDATE upsert behaviour recorded under DEF-008.</t>
+        </is>
+      </c>
+      <c r="K29" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L29" s="3" t="inlineStr">
+        <is>
+          <t>Project owner</t>
+        </is>
+      </c>
+      <c r="M29" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
     </row>
     <row r="30" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="2" t="s">
@@ -2848,10 +2880,26 @@
       <c r="I31" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="J31" s="3"/>
-      <c r="K31" s="6"/>
-      <c r="L31" s="3"/>
-      <c r="M31" s="3"/>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>Clicking directly into any cell of the Slip History grid did not enter an editable state and no text could be typed.</t>
+        </is>
+      </c>
+      <c r="K31" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L31" s="3" t="inlineStr">
+        <is>
+          <t>Project owner</t>
+        </is>
+      </c>
+      <c r="M31" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
     </row>
     <row r="32" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="2" t="s">
@@ -2930,10 +2978,26 @@
       <c r="I33" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="J33" s="3"/>
-      <c r="K33" s="6"/>
-      <c r="L33" s="3"/>
-      <c r="M33" s="3"/>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>Setting the date range to 8 August returned no rows; 10 August returned slip 3; a range spanning both returned slip 3. Only slips falling inside the selected range were shown.</t>
+        </is>
+      </c>
+      <c r="K33" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L33" s="3" t="inlineStr">
+        <is>
+          <t>Project owner</t>
+        </is>
+      </c>
+      <c r="M33" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
     </row>
     <row r="34" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="2" t="s">

--- a/docs/Test_Case_Matrix.xlsx
+++ b/docs/Test_Case_Matrix.xlsx
@@ -3293,10 +3293,26 @@
       <c r="I39" s="3" t="s">
         <v>230</v>
       </c>
-      <c r="J39" s="3"/>
-      <c r="K39" s="6"/>
-      <c r="L39" s="3"/>
-      <c r="M39" s="3"/>
+      <c r="J39" s="3" t="inlineStr">
+        <is>
+          <t>33 unprinted drafts were created. Beyond roughly 28 tiles the panel became scrollable, a scrollbar appeared on the right, and every tile from slip 5 through slip 33 remained reachable by scrolling. No tiles were clipped or lost off-screen.</t>
+        </is>
+      </c>
+      <c r="K39" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L39" s="3" t="inlineStr">
+        <is>
+          <t>Project owner</t>
+        </is>
+      </c>
+      <c r="M39" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
     </row>
     <row r="40" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="2" t="s">
@@ -3326,10 +3342,26 @@
       <c r="I40" s="3" t="s">
         <v>236</v>
       </c>
-      <c r="J40" s="3"/>
-      <c r="K40" s="6"/>
-      <c r="L40" s="3"/>
-      <c r="M40" s="3"/>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t>The Backups folder held a file named WeighbridgeData_20260811_082055.db stamped 8/11/2026 8:20 AM, created by that morning's launch. Every backup taken since the DEF-018 fix carries a Date modified matching its filename timestamp, while the older pre-fix files still show the mismatch that defect described - for example WeighbridgeData_20260805_080052.db stamped 14 July.</t>
+        </is>
+      </c>
+      <c r="K40" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L40" s="3" t="inlineStr">
+        <is>
+          <t>Project owner</t>
+        </is>
+      </c>
+      <c r="M40" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
     </row>
     <row r="41" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="2" t="s">
@@ -3359,10 +3391,26 @@
       <c r="I41" s="3" t="s">
         <v>241</v>
       </c>
-      <c r="J41" s="3"/>
-      <c r="K41" s="6"/>
-      <c r="L41" s="3"/>
-      <c r="M41" s="3"/>
+      <c r="J41" s="3" t="inlineStr">
+        <is>
+          <t>Backup Now opened a Save Database Backup dialog defaulting to a .db filename. A destination outside the application folder was chosen and the file saved, with a Backup Complete message confirming the full path it was written to.</t>
+        </is>
+      </c>
+      <c r="K41" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L41" s="3" t="inlineStr">
+        <is>
+          <t>Project owner</t>
+        </is>
+      </c>
+      <c r="M41" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
     </row>
     <row r="42" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="2" t="inlineStr">

--- a/docs/Test_Case_Matrix.xlsx
+++ b/docs/Test_Case_Matrix.xlsx
@@ -1361,7 +1361,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:M47"/>
+  <dimension ref="A1:M49"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="9"/>
@@ -2847,10 +2847,26 @@
       <c r="I30" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="J30" s="3"/>
-      <c r="K30" s="6"/>
-      <c r="L30" s="3"/>
-      <c r="M30" s="3"/>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The Print Measuring Grid button sent the job and the ruled calibration sheet printed on the active printer and paper profile -- the 10 mm grid with 5 mm ticks along the top and left edges, the page and margin boundaries and the crosshairs at the margin corners and centre, drawn from the driver's own PageBounds and MarginBounds so the sheet can be measured against a ruler to find the mechanical offset.</t>
+        </is>
+      </c>
+      <c r="K30" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pass</t>
+        </is>
+      </c>
+      <c r="L30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Project owner</t>
+        </is>
+      </c>
+      <c r="M30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-11</t>
+        </is>
+      </c>
     </row>
     <row r="31" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="2" t="s">
@@ -3830,6 +3846,149 @@
       <c r="M47" s="3" t="inlineStr">
         <is>
           <t>2026-08-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-047</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Main Page</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tile Display chooses which fields the tiles show, and a later rename appears at once</t>
+        </is>
+      </c>
+      <c r="D48" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FT / BVA / REG</t>
+        </is>
+      </c>
+      <c r="E48" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Medium</t>
+        </is>
+      </c>
+      <c r="F48" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">At least one unprinted slip exists and field labels have been configured</t>
+        </is>
+      </c>
+      <c r="G48" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. On the Main Page click Tile Display
+2. Try to tick five fields
+3. Reduce the selection to four -- Truck Reg, Company, Destination and Tons -- and Save
+4. Check the headings and values on the tiles
+5. Open Customize Slips, rename one of the four and Save
+6. Return to the Main Page without reopening Tile Display</t>
+        </is>
+      </c>
+      <c r="H48" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N/A</t>
+        </is>
+      </c>
+      <c r="I48" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No more than four fields can be chosen, the tiles show the operator's own headings against each slip's data, and renaming a chosen field updates the tiles immediately.</t>
+        </is>
+      </c>
+      <c r="J48" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A fifth tick was refused with a warning message. The four chosen fields appeared on every tile with the configured headings and the matching slip values, including tiles that were already on screen. Renaming Field10 from 'Compony' to 'Client' in Customize Slips left the tiles reading 'Client: RGN-ORE' the moment the Main Page came back, with no need to reopen Tile Display.</t>
+        </is>
+      </c>
+      <c r="K48" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pass</t>
+        </is>
+      </c>
+      <c r="L48" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Project owner</t>
+        </is>
+      </c>
+      <c r="M48" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-048</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Customize Slips</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Renaming a field warns which labels change and everywhere the new wording appears</t>
+        </is>
+      </c>
+      <c r="D49" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FT</t>
+        </is>
+      </c>
+      <c r="E49" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Medium</t>
+        </is>
+      </c>
+      <c r="F49" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The database exists and field labels have been configured</t>
+        </is>
+      </c>
+      <c r="G49" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Open Customize Slips from the Main Page
+2. Change the label of a field -- Field 10 from 'Compony' to 'Client'
+3. Click Save
+4. Read the confirmation
+5. Click OK to commit</t>
+        </is>
+      </c>
+      <c r="H49" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N/A</t>
+        </is>
+      </c>
+      <c r="I49" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A confirmation names every changed label as old to new and lists every place the new wording will be used, making clear what is not affected. Cancel abandons the rename; OK commits it.</t>
+        </is>
+      </c>
+      <c r="J49" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The 'Renaming Fields' dialog listed Field10: 'Compony' to 'Client' and enumerated the Create Slip form, the Slip History grid, its filters and the View and Edit tabs, the printed slip, the Excel headings, the Main Page tiles, the daily summary breakdown and the Manage Lookups selector. It also stated that recorded slips are unchanged because a slip stores the value not the label, and that dropdown suggestions do not follow the rename -- the open DEF-030 behaviour. OK committed the change.</t>
+        </is>
+      </c>
+      <c r="K49" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pass</t>
+        </is>
+      </c>
+      <c r="L49" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Project owner</t>
+        </is>
+      </c>
+      <c r="M49" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-11</t>
         </is>
       </c>
     </row>

--- a/docs/Test_Case_Matrix.xlsx
+++ b/docs/Test_Case_Matrix.xlsx
@@ -1361,7 +1361,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:M49"/>
+  <dimension ref="A1:M53"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="9"/>
@@ -3991,6 +3991,225 @@
           <t xml:space="preserve">2026-08-11</t>
         </is>
       </c>
+    </row>
+    <row r="50" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-049</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Customize Slips</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A rename moves the field to a different suggestion list, and renaming back restores the first one</t>
+        </is>
+      </c>
+      <c r="D50" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FT / REG</t>
+        </is>
+      </c>
+      <c r="E50" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">High</t>
+        </is>
+      </c>
+      <c r="F50" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A field has collected at least two suggestion values</t>
+        </is>
+      </c>
+      <c r="G50" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Note the dropdown suggestions on a field, for example Destination
+2. Open Customize Slips and rename it to a label never used before
+3. Save, open Create Slip and drop the field down
+4. Rename it back to the original label and Save
+5. Open Create Slip and drop it down again</t>
+        </is>
+      </c>
+      <c r="H50" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N/A</t>
+        </is>
+      </c>
+      <c r="I50" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Under the new label the dropdown is empty, because that name has no list yet. Renaming back brings the original suggestions back unchanged. This is the defect: the list follows the label, so it can no longer offer values from the wrong domain.</t>
+        </is>
+      </c>
+      <c r="J50" s="3"/>
+      <c r="K50" s="6"/>
+      <c r="L50" s="3"/>
+      <c r="M50" s="3"/>
+    </row>
+    <row r="51" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-050</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Create Slip</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Suggestions are collected when a slip is written, not when a box is left</t>
+        </is>
+      </c>
+      <c r="D51" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FT</t>
+        </is>
+      </c>
+      <c r="E51" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Medium</t>
+        </is>
+      </c>
+      <c r="F51" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">At least one field shows a dropdown</t>
+        </is>
+      </c>
+      <c r="G51" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Open Create Slip, type a new value into a lookup field and tab out of it
+2. Cancel the form without saving
+3. Re-open Create Slip and drop that field down
+4. Enter a slip properly and click Save
+5. Open Create Slip again and drop the same field down</t>
+        </is>
+      </c>
+      <c r="H51" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N/A</t>
+        </is>
+      </c>
+      <c r="I51" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The abandoned value is absent after step 3 -- nothing was written, so nothing was learned. The saved value is present after step 5.</t>
+        </is>
+      </c>
+      <c r="J51" s="3"/>
+      <c r="K51" s="6"/>
+      <c r="L51" s="3"/>
+      <c r="M51" s="3"/>
+    </row>
+    <row r="52" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-051</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manage Lookups</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lists can be cleared or deleted, and lists no field uses are still shown</t>
+        </is>
+      </c>
+      <c r="D52" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FT</t>
+        </is>
+      </c>
+      <c r="E52" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Medium</t>
+        </is>
+      </c>
+      <c r="F52" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">At least one list holds values, and one field has been renamed away from a label that has a list</t>
+        </is>
+      </c>
+      <c r="G52" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Open Manage Lookups and read the selector
+2. Select a list and click Clear List
+3. Re-select it and confirm it is still listed, with no entries
+4. Select a list marked as used by no field and click Delete List
+5. Re-open Manage Lookups</t>
+        </is>
+      </c>
+      <c r="H52" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N/A</t>
+        </is>
+      </c>
+      <c r="I52" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The selector shows every list with its entry count, marking those no field currently points at. Clear empties a list but keeps it; Delete removes it entirely. Neither touches any recorded slip.</t>
+        </is>
+      </c>
+      <c r="J52" s="3"/>
+      <c r="K52" s="6"/>
+      <c r="L52" s="3"/>
+      <c r="M52" s="3"/>
+    </row>
+    <row r="53" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-052</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Create Slip</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A new database starts with no suggestion lists at all</t>
+        </is>
+      </c>
+      <c r="D53" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FT</t>
+        </is>
+      </c>
+      <c r="E53" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Medium</t>
+        </is>
+      </c>
+      <c r="F53" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No WeighbridgeData.db exists in the application folder</t>
+        </is>
+      </c>
+      <c r="G53" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Delete the database and complete First-Time Setup
+2. Open Manage Lookups
+3. Open Create Slip and drop down any lookup field
+4. Save a slip, then re-open Create Slip and drop the same field down</t>
+        </is>
+      </c>
+      <c r="H53" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N/A</t>
+        </is>
+      </c>
+      <c r="I53" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manage Lookups reports that no lists exist yet rather than showing empty named lists, and every dropdown is empty. After the first saved slip the entered values appear as suggestions. Nothing is seeded at setup.</t>
+        </is>
+      </c>
+      <c r="J53" s="3"/>
+      <c r="K53" s="6"/>
+      <c r="L53" s="3"/>
+      <c r="M53" s="3"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/docs/Test_Case_Matrix.xlsx
+++ b/docs/Test_Case_Matrix.xlsx
@@ -4042,10 +4042,26 @@
           <t xml:space="preserve">Under the new label the dropdown is empty, because that name has no list yet. Renaming back brings the original suggestions back unchanged. This is the defect: the list follows the label, so it can no longer offer values from the wrong domain.</t>
         </is>
       </c>
-      <c r="J50" s="3"/>
-      <c r="K50" s="6"/>
-      <c r="L50" s="3"/>
-      <c r="M50" s="3"/>
+      <c r="J50" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Field10 was renamed between Customer and Client several times. Under a label never used before the dropdown was empty; printing a slip under that label created the list and captured its values. Renaming back brought the earlier list's entries back into the Create Slip dropdown unchanged, while the other list stayed intact and was shown in Manage Lookups marked as used by no field. Re-entering values a list already held produced no duplicates. Confirmed in the database: nine lists all stamped 2026-08-11 14:40:49 from the first saved slip, each holding only its own field's values, with no lookup table remaining from the old slot-bound schema.</t>
+        </is>
+      </c>
+      <c r="K50" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pass</t>
+        </is>
+      </c>
+      <c r="L50" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Project owner</t>
+        </is>
+      </c>
+      <c r="M50" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-11</t>
+        </is>
+      </c>
     </row>
     <row r="51" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="2" t="inlineStr">
@@ -4152,10 +4168,26 @@
           <t xml:space="preserve">The selector shows every list with its entry count, marking those no field currently points at. Clear empties a list but keeps it; Delete removes it entirely. Neither touches any recorded slip.</t>
         </is>
       </c>
-      <c r="J52" s="3"/>
-      <c r="K52" s="6"/>
-      <c r="L52" s="3"/>
-      <c r="M52" s="3"/>
+      <c r="J52" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The selector listed every list with its entry count and marked the ones no field points at, for example 'Customer (1 entry) - no field uses this label' after Field10 was renamed to Client. An entry added directly through Manage Lookups on the Block Nr list appeared immediately in that field's Create Slip dropdown, giving BL8 and BL9. Clear List emptied a list but left it in the selector with no entries, and the corresponding dropdown went empty. Delete List removed it entirely. After a delete, saving a slip recreated the list under the same name holding only the new value - confirmed in the database, where the rebuilt Customer list is stamped 15:01:49, one second after slip 5's row was written.</t>
+        </is>
+      </c>
+      <c r="K52" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pass</t>
+        </is>
+      </c>
+      <c r="L52" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Project owner</t>
+        </is>
+      </c>
+      <c r="M52" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-11</t>
+        </is>
+      </c>
     </row>
     <row r="53" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="2" t="inlineStr">
@@ -4206,10 +4238,26 @@
           <t xml:space="preserve">Manage Lookups reports that no lists exist yet rather than showing empty named lists, and every dropdown is empty. After the first saved slip the entered values appear as suggestions. Nothing is seeded at setup.</t>
         </is>
       </c>
-      <c r="J53" s="3"/>
-      <c r="K53" s="6"/>
-      <c r="L53" s="3"/>
-      <c r="M53" s="3"/>
+      <c r="J53" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">On the fresh database Manage Lookups reported 'No suggestion lists yet' with the selector and the add and delete controls disabled, rather than showing nine empty named lists, and every Create Slip dropdown was empty. Saving the first slip without printing it created one list per labelled field, each holding that slip's value - nine lists, all stamped 2026-08-11 14:40:49, matching the slip's own CreatedAt. Nothing is seeded at setup. Noted during the run: because a list does not exist until a value is saved under it, entries cannot be added through Manage Lookups ahead of the first slip.</t>
+        </is>
+      </c>
+      <c r="K53" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pass</t>
+        </is>
+      </c>
+      <c r="L53" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Project owner</t>
+        </is>
+      </c>
+      <c r="M53" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-11</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/docs/Test_Case_Matrix.xlsx
+++ b/docs/Test_Case_Matrix.xlsx
@@ -4113,10 +4113,26 @@
           <t xml:space="preserve">The abandoned value is absent after step 3 -- nothing was written, so nothing was learned. The saved value is present after step 5.</t>
         </is>
       </c>
-      <c r="J51" s="3"/>
-      <c r="K51" s="6"/>
-      <c r="L51" s="3"/>
-      <c r="M51" s="3"/>
+      <c r="J51" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A value typed into a lookup field and tabbed out of, on a form then closed with Cancel, was absent from that field's dropdown when Create Slip was re-opened -- the slip was never written, so nothing was learned from it. Values from slips that were written did appear, proven repeatedly across the DEF-030 run: all nine lists carry CreatedAt 14:40:49, matching the first slip's own CreatedAt at the moment it was Saved rather than printed, and the Customer list rebuilt after a delete is stamped 15:01:49 against slip 5's row at 15:01:48. Printing counts as writing the slip: slip 2 was sent to the printer without being Saved first and its values were captured, since the print path commits the slip before the preview opens.</t>
+        </is>
+      </c>
+      <c r="K51" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pass</t>
+        </is>
+      </c>
+      <c r="L51" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Project owner</t>
+        </is>
+      </c>
+      <c r="M51" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-11</t>
+        </is>
+      </c>
     </row>
     <row r="52" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="2" t="inlineStr">
@@ -4240,7 +4256,7 @@
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">On the fresh database Manage Lookups reported 'No suggestion lists yet' with the selector and the add and delete controls disabled, rather than showing nine empty named lists, and every Create Slip dropdown was empty. Saving the first slip without printing it created one list per labelled field, each holding that slip's value - nine lists, all stamped 2026-08-11 14:40:49, matching the slip's own CreatedAt. Nothing is seeded at setup. Noted during the run: because a list does not exist until a value is saved under it, entries cannot be added through Manage Lookups ahead of the first slip.</t>
+          <t xml:space="preserve">On the fresh database Manage Lookups reported 'No suggestion lists yet' with the selector and the add and delete controls disabled, rather than showing nine empty named lists, and every Create Slip dropdown was empty. Saving the first slip without printing it created one list per labelled field, each holding that slip's value -- nine lists, all stamped 2026-08-11 14:40:49, matching the slip's own CreatedAt. Nothing is seeded at setup. Noted during the run: because a list does not exist until a value is saved under it, entries cannot be added through Manage Lookups ahead of the first slip. Raised with the project owner on 2026-08-11 and kept as designed -- a list existing is meant to be evidence that a slip put something in it, and no other route should create one.</t>
         </is>
       </c>
       <c r="K53" s="6" t="inlineStr">

--- a/docs/Test_Case_Matrix.xlsx
+++ b/docs/Test_Case_Matrix.xlsx
@@ -1361,7 +1361,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:M53"/>
+  <dimension ref="A1:M54"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="9"/>
@@ -4270,6 +4270,78 @@
         </is>
       </c>
       <c r="M53" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-053</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Database Schema</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A database from an earlier build upgrades in place without losing a record</t>
+        </is>
+      </c>
+      <c r="D54" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">REG / FT</t>
+        </is>
+      </c>
+      <c r="E54" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">High</t>
+        </is>
+      </c>
+      <c r="F54" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A database created by a pre-3-July build is in the application folder, holding slips plus the nine legacy lookup tables, the FieldConfig.LookupTable column and the superseded calibration keys</t>
+        </is>
+      </c>
+      <c r="G54" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Put the older database in the application folder
+2. Launch the application
+3. Check Slip History for both the Printed and Voided views
+4. Open Printer Settings, select the active preset and open Calibration
+5. Open Customize Slips and Manage Lookups
+6. Inspect the database file</t>
+        </is>
+      </c>
+      <c r="H54" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N/A</t>
+        </is>
+      </c>
+      <c r="I54" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The application opens straight to the Main Page with no First-Time Setup. Every slip, bill number, void reason, printer profile and field label survives exactly as it was. Superseded schema is removed: the nine lookup tables, the LookupTable column and the three orphaned GlobalSettings keys. Calibration still reports the profile's own values, not the stale global ones. Settings the older build never had fall back to a sensible default rather than failing.</t>
+        </is>
+      </c>
+      <c r="J54" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Launched straight to the Main Page. Slip History showed 8 printed slips totalling 183.474 t and 4 voided slips with their reasons and Voided At dates, and the 4 remaining drafts appeared as Main Page tiles - 16 slips, SlipID 1 to 16, no gaps. Print Calibration on the active Default preset read scale 1.95, X -1.0, Y 0.0, the profile's own values; the stale 2.75, 0 and -1.5 were gone. All three presets, the Small151x151 paper profile, the ten field labels including Field10 as 'Client', and the summary grouping by Destination were unchanged. The database confirmed 3 orphaned keys removed, 9 legacy tables dropped with their 28 values, and the LookupTable column dropped, with slip count, distinct bill numbers, max SlipID and total printed tons all identical before and after. Manage Lookups was empty, which is the agreed cost of the DEF-030 upgrade. TileFields did not exist in this database and the tiles fell back to Truck Reg and Tons rather than failing.</t>
+        </is>
+      </c>
+      <c r="K54" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pass</t>
+        </is>
+      </c>
+      <c r="L54" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Project owner</t>
+        </is>
+      </c>
+      <c r="M54" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-08-11</t>
         </is>

--- a/docs/Test_Case_Matrix.xlsx
+++ b/docs/Test_Case_Matrix.xlsx
@@ -1361,7 +1361,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:M54"/>
+  <dimension ref="A1:M59"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="9"/>
@@ -4344,6 +4344,326 @@
       <c r="M54" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-054</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Printing</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Copies on one page can be arranged side by side, stacked, or as a grid</t>
+        </is>
+      </c>
+      <c r="D55" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FT / REG</t>
+        </is>
+      </c>
+      <c r="E55" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Medium</t>
+        </is>
+      </c>
+      <c r="F55" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A preset exists and the paper is A4 or larger, so multiple copies are available</t>
+        </is>
+      </c>
+      <c r="G55" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Open Printer Settings and click Calibration Page
+2. Set Copies to 2 and Arrangement to Side by side, check the preview
+3. Change Arrangement to Stacked and check the preview again
+4. Print a test page and compare it against the preview
+5. Set Copies to 4 and confirm Grid (2 x 2) becomes available
+6. Save, reopen the screen and confirm the choice was kept</t>
+        </is>
+      </c>
+      <c r="H55" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N/A</t>
+        </is>
+      </c>
+      <c r="I55" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The preview and the printed sheet show the chosen arrangement, the cut lines run the matching way, Grid is offered only at 4 copies, the control is disabled at 1 copy, and the choice is stored against the preset.</t>
+        </is>
+      </c>
+      <c r="J55" s="3"/>
+      <c r="K55" s="6"/>
+      <c r="L55" s="3"/>
+      <c r="M55" s="3"/>
+    </row>
+    <row r="56" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-055</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Printing</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Printing to PDF offers a file name already filled in</t>
+        </is>
+      </c>
+      <c r="D56" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FT</t>
+        </is>
+      </c>
+      <c r="E56" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Medium</t>
+        </is>
+      </c>
+      <c r="F56" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Microsoft Print to PDF is the selected printer</t>
+        </is>
+      </c>
+      <c r="G56" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Create a slip, entering a Truck Reg
+2. Click Print and confirm the preview
+3. Read the File name box in the Save dialog
+4. Save, then repeat with a second slip and check the folder it opens in</t>
+        </is>
+      </c>
+      <c r="H56" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N/A</t>
+        </is>
+      </c>
+      <c r="I56" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The Save dialog opens with the bill number and the leading field's value already in the File name box, still editable, and only one dialog appears.</t>
+        </is>
+      </c>
+      <c r="J56" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The Save dialog opened with the name already filled in - bill number followed by the truck registration, matching the job name shown in the Printing window. Only one dialog appeared; the driver did not prompt a second time.</t>
+        </is>
+      </c>
+      <c r="K56" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pass</t>
+        </is>
+      </c>
+      <c r="L56" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Project owner</t>
+        </is>
+      </c>
+      <c r="M56" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-056</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Slip Lifecycle</t>
+        </is>
+      </c>
+      <c r="C57" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cancelling the PDF Save dialog leaves the slip an unprinted draft</t>
+        </is>
+      </c>
+      <c r="D57" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NT</t>
+        </is>
+      </c>
+      <c r="E57" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Critical</t>
+        </is>
+      </c>
+      <c r="F57" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Microsoft Print to PDF is the selected printer and a draft slip is open</t>
+        </is>
+      </c>
+      <c r="G57" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Create a slip and click Print
+2. Confirm the print preview
+3. Click Cancel on the Save dialog
+4. Return to the Main Page and look for the slip's tile
+5. Check Slip History for the same slip</t>
+        </is>
+      </c>
+      <c r="H57" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N/A</t>
+        </is>
+      </c>
+      <c r="I57" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The slip is still an unprinted draft and its tile is still on the Main Page. Nothing was produced, so nothing may be recorded as printed - a printed slip can never be returned to draft.</t>
+        </is>
+      </c>
+      <c r="J57" s="3"/>
+      <c r="K57" s="6"/>
+      <c r="L57" s="3"/>
+      <c r="M57" s="3"/>
+    </row>
+    <row r="58" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-057</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Printing</t>
+        </is>
+      </c>
+      <c r="C58" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The company logo prints, and survives the file it came from being moved</t>
+        </is>
+      </c>
+      <c r="D58" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FT / REG</t>
+        </is>
+      </c>
+      <c r="E58" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">High</t>
+        </is>
+      </c>
+      <c r="F58" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">An image file is available to select as the logo</t>
+        </is>
+      </c>
+      <c r="G58" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Open Customize Slips and choose a logo image
+2. Print a slip and check the letterhead
+3. Move, rename or delete the original image file
+4. Print another slip</t>
+        </is>
+      </c>
+      <c r="H58" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N/A</t>
+        </is>
+      </c>
+      <c r="I58" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The logo prints on both slips. Once chosen it no longer depends on the original file existing, so it also survives the system being handed to another machine.</t>
+        </is>
+      </c>
+      <c r="J58" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The logo printed on the slip as expected.</t>
+        </is>
+      </c>
+      <c r="K58" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pass</t>
+        </is>
+      </c>
+      <c r="L58" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Project owner</t>
+        </is>
+      </c>
+      <c r="M58" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-058</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Printer Settings</t>
+        </is>
+      </c>
+      <c r="C59" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Every field on the Printer Settings screen is separate and inside the form</t>
+        </is>
+      </c>
+      <c r="D59" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FT</t>
+        </is>
+      </c>
+      <c r="E59" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Low</t>
+        </is>
+      </c>
+      <c r="F59" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The database exists and a preset is active</t>
+        </is>
+      </c>
+      <c r="G59" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Open Printer Settings
+2. Look at Company Name and Slip Length
+3. Check that no control runs past the right edge of the form</t>
+        </is>
+      </c>
+      <c r="H59" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N/A</t>
+        </is>
+      </c>
+      <c r="I59" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Each field has its own box with clear space between it and the next, and every control sits inside the form at the display's scaling.</t>
+        </is>
+      </c>
+      <c r="J59" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The two boxes are now clearly separate and both sit well inside the form.</t>
+        </is>
+      </c>
+      <c r="K59" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pass</t>
+        </is>
+      </c>
+      <c r="L59" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Project owner</t>
+        </is>
+      </c>
+      <c r="M59" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-13</t>
         </is>
       </c>
     </row>

--- a/docs/Test_Case_Matrix.xlsx
+++ b/docs/Test_Case_Matrix.xlsx
@@ -4523,10 +4523,26 @@
           <t xml:space="preserve">The slip is still an unprinted draft and its tile is still on the Main Page. Nothing was produced, so nothing may be recorded as printed - a printed slip can never be returned to draft.</t>
         </is>
       </c>
-      <c r="J57" s="3"/>
-      <c r="K57" s="6"/>
-      <c r="L57" s="3"/>
-      <c r="M57" s="3"/>
+      <c r="J57" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cancelling the Save dialog left the slip an unprinted draft - its tile stayed on the Main Page and Slip History did not list it among the printed slips. Nothing was produced and nothing was recorded as printed, so the slip remained editable and voidable rather than being frozen into a printed state with no document behind it.</t>
+        </is>
+      </c>
+      <c r="K57" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pass</t>
+        </is>
+      </c>
+      <c r="L57" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Project owner</t>
+        </is>
+      </c>
+      <c r="M57" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-17</t>
+        </is>
+      </c>
     </row>
     <row r="58" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="2" t="inlineStr">

--- a/docs/Test_Case_Matrix.xlsx
+++ b/docs/Test_Case_Matrix.xlsx
@@ -1361,7 +1361,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:M59"/>
+  <dimension ref="A1:M60"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="9"/>
@@ -4398,10 +4398,26 @@
           <t xml:space="preserve">The preview and the printed sheet show the chosen arrangement, the cut lines run the matching way, Grid is offered only at 4 copies, the control is disabled at 1 copy, and the choice is stored against the preset.</t>
         </is>
       </c>
-      <c r="J55" s="3"/>
-      <c r="K55" s="6"/>
-      <c r="L55" s="3"/>
-      <c r="M55" s="3"/>
+      <c r="J55" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">All three arrangements were exercised on A4. Side by side produced two columns with a vertical cut line; Stacked produced two rows with a horizontal one, each slip laid out wide and short rather than a tall slip squashed sideways; Grid produced two across and two down; four copies stacked produced four rows with three cut lines. Selecting Grid at four copies and then dropping to two removed Grid from the list and fell back to Side by side rather than leaving a dead selection, and Arrangement was correctly disabled at one copy. Printed PDF output matched the preview in each case. Noted during the run: side by side halves the cell width, so it needs a smaller font scale than stacked before the company name fits.</t>
+        </is>
+      </c>
+      <c r="K55" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pass</t>
+        </is>
+      </c>
+      <c r="L55" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Project owner</t>
+        </is>
+      </c>
+      <c r="M55" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-17</t>
+        </is>
+      </c>
     </row>
     <row r="56" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="2" t="inlineStr">
@@ -4680,6 +4696,77 @@
       <c r="M59" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-08-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-059</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Printing</t>
+        </is>
+      </c>
+      <c r="C60" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Landscape prints on a landscape sheet, with the layout matching</t>
+        </is>
+      </c>
+      <c r="D60" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FT / REG</t>
+        </is>
+      </c>
+      <c r="E60" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">High</t>
+        </is>
+      </c>
+      <c r="F60" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A4 paper, and a printer or Microsoft Print to PDF available</t>
+        </is>
+      </c>
+      <c r="G60" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Printer Settings: set Orientation to Landscape on the active preset and save
+2. Open the calibration screen and check the shape of the previewed page
+3. Set two copies per page and print to PDF
+4. Open the PDF and check the page shape, not just the content
+5. Repeat the whole sequence with Orientation set to Portrait</t>
+        </is>
+      </c>
+      <c r="H60" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N/A</t>
+        </is>
+      </c>
+      <c r="I60" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The printed sheet takes the chosen orientation, the content is laid out for that shape with nothing running off an edge, and both preview canvases show the same page the printer produces.</t>
+        </is>
+      </c>
+      <c r="J60" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">In Landscape the calibration canvas showed a wide page and the PDF came out on a landscape sheet with both copies complete. In Portrait both the canvas and the PDF were portrait. Tested twice in each orientation, at two and four copies and across all three arrangements. The earlier failure -- a rotated sheet carrying portrait-shaped content, so the second copy fell off the bottom -- did not recur.</t>
+        </is>
+      </c>
+      <c r="K60" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pass</t>
+        </is>
+      </c>
+      <c r="L60" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Project owner</t>
+        </is>
+      </c>
+      <c r="M60" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-17</t>
         </is>
       </c>
     </row>

--- a/docs/Test_Case_Matrix.xlsx
+++ b/docs/Test_Case_Matrix.xlsx
@@ -1361,7 +1361,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:M60"/>
+  <dimension ref="A1:M63"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="9"/>
@@ -4769,6 +4769,202 @@
           <t xml:space="preserve">2026-08-17</t>
         </is>
       </c>
+    </row>
+    <row r="61" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-060</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Backup</t>
+        </is>
+      </c>
+      <c r="C61" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Restore screen lists every backup with what it holds</t>
+        </is>
+      </c>
+      <c r="D61" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FT</t>
+        </is>
+      </c>
+      <c r="E61" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">High</t>
+        </is>
+      </c>
+      <c r="F61" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">At least one backup exists in the Backups folder</t>
+        </is>
+      </c>
+      <c r="G61" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. On the Main Page click Restore Backup
+2. Compare the list against the files in the Backups folder
+3. Check each row reports its age and slip counts
+4. Confirm a damaged copy is shown as unusable and cannot be selected</t>
+        </is>
+      </c>
+      <c r="H61" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N/A</t>
+        </is>
+      </c>
+      <c r="I61" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Every backup is listed with when it was taken, how long ago, how many slips and how many printed, read from the file rather than inferred. A copy that cannot be opened is marked and refused.</t>
+        </is>
+      </c>
+      <c r="J61" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The screen listed eleven backups spanning 12 to 18 August, each showing its timestamp, a plain-language age, slip and printed counts, size and a Readable condition, matching the files in C:\ProgramData\UitvalSlips\Backups exactly. Selecting a row reported what that copy holds above the list. The damaged-file path was not exercised, no corrupt backup being available.</t>
+        </is>
+      </c>
+      <c r="K61" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pass</t>
+        </is>
+      </c>
+      <c r="L61" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Project owner</t>
+        </is>
+      </c>
+      <c r="M61" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-061</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Backup</t>
+        </is>
+      </c>
+      <c r="C62" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Restoring rewinds the records and keeps the database it replaced</t>
+        </is>
+      </c>
+      <c r="D62" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FT / REG</t>
+        </is>
+      </c>
+      <c r="E62" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Critical</t>
+        </is>
+      </c>
+      <c r="F62" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A backup exists that is older than the current database</t>
+        </is>
+      </c>
+      <c r="G62" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Note the current slips
+2. Open Restore Backup and choose an older copy
+3. Read the confirmation and accept
+4. Let the program close, start it again
+5. Check the slips and the data folder</t>
+        </is>
+      </c>
+      <c r="H62" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N/A</t>
+        </is>
+      </c>
+      <c r="I62" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The records return to their state at the moment that copy was taken, the program closes and reopens cleanly, and the database that was replaced is kept rather than deleted.</t>
+        </is>
+      </c>
+      <c r="J62" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Restored to the copy taken 2026-08-17 at 18:16, which the screen reported as holding 3 slips. After restarting, Slip History showed 2 printed slips and the third appeared as an unprinted draft on the Main Page, totalling the 3 reported. The replaced database was kept as WeighbridgeData_replaced_20260818_101851.db in C:\ProgramData\UitvalSlips, confirming the previous records were set aside rather than destroyed.</t>
+        </is>
+      </c>
+      <c r="K62" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pass</t>
+        </is>
+      </c>
+      <c r="L62" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Project owner</t>
+        </is>
+      </c>
+      <c r="M62" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-062</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Backup</t>
+        </is>
+      </c>
+      <c r="C63" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A committed change triggers a backup, throttled to the interval</t>
+        </is>
+      </c>
+      <c r="D63" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FT</t>
+        </is>
+      </c>
+      <c r="E63" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">High</t>
+        </is>
+      </c>
+      <c r="F63" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The application is running and the database already exists</t>
+        </is>
+      </c>
+      <c r="G63" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Note the newest file in the Backups folder
+2. Save a new slip
+3. Check the Backups folder for a new copy
+4. Save another slip immediately and confirm no second copy appears
+5. Wait past the fifteen-minute interval, save again, confirm a copy appears</t>
+        </is>
+      </c>
+      <c r="H63" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N/A</t>
+        </is>
+      </c>
+      <c r="I63" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A saved, printed, edited or voided slip produces a backup, but no more often than once every fifteen minutes. Startup always takes one regardless.</t>
+        </is>
+      </c>
+      <c r="J63" s="3"/>
+      <c r="K63" s="6"/>
+      <c r="L63" s="3"/>
+      <c r="M63" s="3"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/docs/Test_Case_Matrix.xlsx
+++ b/docs/Test_Case_Matrix.xlsx
@@ -1361,7 +1361,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:M63"/>
+  <dimension ref="A1:M66"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="9"/>
@@ -4965,6 +4965,215 @@
       <c r="K63" s="6"/>
       <c r="L63" s="3"/>
       <c r="M63" s="3"/>
+    </row>
+    <row r="64" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-063</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Licensing</t>
+        </is>
+      </c>
+      <c r="C64" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A licence issued for this computer activates on it</t>
+        </is>
+      </c>
+      <c r="D64" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FT</t>
+        </is>
+      </c>
+      <c r="E64" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Critical</t>
+        </is>
+      </c>
+      <c r="F64" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The program is built and no valid licence is present</t>
+        </is>
+      </c>
+      <c r="G64" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Start the program and read the machine code on the licence screen
+2. Run New-UitvalLicence.ps1 with exactly that code
+3. Paste the returned licence into the box
+4. Click Activate</t>
+        </is>
+      </c>
+      <c r="H64" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N/A</t>
+        </is>
+      </c>
+      <c r="I64" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The licence is accepted, names the company and site, and the program restarts licensed. A licence file appears in the data folder.</t>
+        </is>
+      </c>
+      <c r="J64" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The code 2951E-3EA16-B7899-0BACE-E7DC6-F62B2 was read from the screen and a licence issued against it. Activate accepted it and confirmed 'Licensed to: Uitval Gronde Pty (Ltd), Site: Main office, Issued: 2026-08-19'. licence.lic was written to C:\ProgramData\UitvalSlips with its signature block intact. This is the case that DEF-041 had made impossible.</t>
+        </is>
+      </c>
+      <c r="K64" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pass</t>
+        </is>
+      </c>
+      <c r="L64" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Project owner</t>
+        </is>
+      </c>
+      <c r="M64" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-064</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Licensing</t>
+        </is>
+      </c>
+      <c r="C65" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Without a licence the records stay fully reachable</t>
+        </is>
+      </c>
+      <c r="D65" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FT / NT</t>
+        </is>
+      </c>
+      <c r="E65" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Critical</t>
+        </is>
+      </c>
+      <c r="F65" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A licensed installation holding at least one printed slip</t>
+        </is>
+      </c>
+      <c r="G65" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Close the program and rename licence.lic in the data folder
+2. Start the program
+3. Try to create a new slip, and open an existing one from its tile
+4. Open Slip History, search it, and export to Excel</t>
+        </is>
+      </c>
+      <c r="H65" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N/A</t>
+        </is>
+      </c>
+      <c r="I65" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">New slips are refused and the restriction is stated plainly, while opening, searching, reprinting and exporting existing slips all continue to work. The operator's records are never held behind the licence.</t>
+        </is>
+      </c>
+      <c r="J65" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The Main Page showed the read-only banner, a Licence button appeared, and New Slip was disabled and relabelled 'New Slip (not licensed)'. Opening the existing slip from its tile displayed all its data and refused only on save or print, with a message explaining that recorded slips are unaffected. Slip History opened and searched normally and Export produced Slips_Printed_Export_20260819. Nothing about the records was withheld.</t>
+        </is>
+      </c>
+      <c r="K65" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pass</t>
+        </is>
+      </c>
+      <c r="L65" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Project owner</t>
+        </is>
+      </c>
+      <c r="M65" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-065</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Licensing</t>
+        </is>
+      </c>
+      <c r="C66" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The licence persists across a restart and recovers when restored</t>
+        </is>
+      </c>
+      <c r="D66" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">REG</t>
+        </is>
+      </c>
+      <c r="E66" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">High</t>
+        </is>
+      </c>
+      <c r="F66" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A licensed installation</t>
+        </is>
+      </c>
+      <c r="G66" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Close and reopen the program
+2. Rename licence.lic away, start, and confirm read-only
+3. Rename it back and start again</t>
+        </is>
+      </c>
+      <c r="H66" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N/A</t>
+        </is>
+      </c>
+      <c r="I66" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A licensed machine stays licensed across restarts without re-activation, and restoring a renamed licence file returns it to normal.</t>
+        </is>
+      </c>
+      <c r="J66" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reopening kept the machine licensed with no banner and no re-activation. With the file renamed away the program came up read-only, and renaming it back restored full function on the next start -- banner gone, Licence button gone, New Slip enabled.</t>
+        </is>
+      </c>
+      <c r="K66" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pass</t>
+        </is>
+      </c>
+      <c r="L66" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Project owner</t>
+        </is>
+      </c>
+      <c r="M66" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-19</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/docs/Test_Case_Matrix.xlsx
+++ b/docs/Test_Case_Matrix.xlsx
@@ -4961,10 +4961,26 @@
           <t xml:space="preserve">A saved, printed, edited or voided slip produces a backup, but no more often than once every fifteen minutes. Startup always takes one regardless.</t>
         </is>
       </c>
-      <c r="J63" s="3"/>
-      <c r="K63" s="6"/>
-      <c r="L63" s="3"/>
-      <c r="M63" s="3"/>
+      <c r="J63" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Before the test the folder held 17 backups, the newest stamped 20260819_095132 at 09:51. Saving a slip produced WeighbridgeData_20260819_130604 at 13:06, taking the folder to 18 - a backup following a committed change rather than a launch, which is what the old startup-only behaviour could not do. Saving a second slip about a minute later produced no further copy: the folder stayed at 18 files with the same newest name, confirming the fifteen-minute throttle holds between changes.</t>
+        </is>
+      </c>
+      <c r="K63" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pass</t>
+        </is>
+      </c>
+      <c r="L63" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Project owner</t>
+        </is>
+      </c>
+      <c r="M63" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-19</t>
+        </is>
+      </c>
     </row>
     <row r="64" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="2" t="inlineStr">

--- a/docs/Test_Case_Matrix.xlsx
+++ b/docs/Test_Case_Matrix.xlsx
@@ -1361,7 +1361,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:M66"/>
+  <dimension ref="A1:M68"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="9"/>
@@ -5186,6 +5186,148 @@
         </is>
       </c>
       <c r="M66" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-066</t>
+        </is>
+      </c>
+      <c r="B67" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Printer Settings</t>
+        </is>
+      </c>
+      <c r="C67" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A margin measured in calibration survives a later Save Configuration</t>
+        </is>
+      </c>
+      <c r="D67" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FT / REG</t>
+        </is>
+      </c>
+      <c r="E67" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">High</t>
+        </is>
+      </c>
+      <c r="F67" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A printer preset exists and is active</t>
+        </is>
+      </c>
+      <c r="G67" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Open Printer Settings and note the Right margin
+2. Click Calibration Page, change Right to a different value, click Save Settings
+3. Confirm Printer Settings now shows the new value rather than the old
+4. Click Save Configuration
+5. Reopen Printer Settings and read the Right margin</t>
+        </is>
+      </c>
+      <c r="H67" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N/A</t>
+        </is>
+      </c>
+      <c r="I67" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Printer Settings reflects the calibrated value as soon as the dialog closes, and Save Configuration preserves it rather than writing back what was on screen beforehand.</t>
+        </is>
+      </c>
+      <c r="J67" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Right was calibrated from 10.0 to 21.0 and saved. Printer Settings came back showing Right 21.0 rather than the 10.0 it had held before, and the stored profile read T 10 / L 10 / R 21 / B 10 with scale 2.35. A real slip printed on the EPSON LX-350 came out correctly positioned against the calibrated margins, which is how the original fault was noticed - the printed output had previously kept reverting to the uncalibrated layout.</t>
+        </is>
+      </c>
+      <c r="K67" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pass</t>
+        </is>
+      </c>
+      <c r="L67" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Project owner</t>
+        </is>
+      </c>
+      <c r="M67" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-067</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Printer Settings</t>
+        </is>
+      </c>
+      <c r="C68" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Both calibration routes address the same preset and say which</t>
+        </is>
+      </c>
+      <c r="D68" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FT / REG</t>
+        </is>
+      </c>
+      <c r="E68" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">High</t>
+        </is>
+      </c>
+      <c r="F68" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A printer preset exists and is active</t>
+        </is>
+      </c>
+      <c r="G68" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Open calibration from Printer Settings, change a value, save
+2. Open calibration from a slip's print preview and compare every field
+3. Change a value there, save
+4. Reopen calibration from Printer Settings and compare again
+5. Read the window title on both routes</t>
+        </is>
+      </c>
+      <c r="H68" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N/A</t>
+        </is>
+      </c>
+      <c r="I68" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Both routes show identical values, write to the same preset, and name that preset in the title so it is never ambiguous which profile is being measured.</t>
+        </is>
+      </c>
+      <c r="J68" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A change made from Printer Settings appeared unchanged in the preview's calibration screen - Right 21.0, scale 1.95, offsets 0.0 and 0.5 - and a change made from the preview appeared in Printer Settings' calibration screen, scale 2.35 and Right 21.0. The stored profile matched both. Both routes titled the window 'Print Calibration - Default (active preset)', where previously one named a preset and the other named nothing.</t>
+        </is>
+      </c>
+      <c r="K68" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pass</t>
+        </is>
+      </c>
+      <c r="L68" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Project owner</t>
+        </is>
+      </c>
+      <c r="M68" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-08-19</t>
         </is>

--- a/docs/Test_Case_Matrix.xlsx
+++ b/docs/Test_Case_Matrix.xlsx
@@ -1361,7 +1361,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:M68"/>
+  <dimension ref="A1:M70"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="9"/>
@@ -5328,6 +5328,147 @@
         </is>
       </c>
       <c r="M68" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-068</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Deployment</t>
+        </is>
+      </c>
+      <c r="C69" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Installing leaves records already on the machine untouched</t>
+        </is>
+      </c>
+      <c r="D69" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FT / REG</t>
+        </is>
+      </c>
+      <c r="E69" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Critical</t>
+        </is>
+      </c>
+      <c r="F69" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The installer is built and the machine already holds slips, a licence and printer calibration</t>
+        </is>
+      </c>
+      <c r="G69" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Note the slip count, the licence state and the calibration values
+2. Run UitvalSlips-Setup, accept the licence, install to Program Files
+3. Start the program from the new shortcut
+4. Compare against what was noted, and check the timestamps in the data folder</t>
+        </is>
+      </c>
+      <c r="H69" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N/A</t>
+        </is>
+      </c>
+      <c r="I69" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The program installs to Program Files while everything in C:\ProgramData\UitvalSlips is left exactly as it was. The installed copy opens already licensed, showing the existing slips and calibration.</t>
+        </is>
+      </c>
+      <c r="J69" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The program installed to C:\Program Files\Uitval Slips with 17 payload files plus its uninstaller, and no database or debug file among them. It opened showing the existing 5 loads and 184.260 t with no licence banner and New Slip enabled, so licence.lic had been picked up rather than reissued. WeighbridgeData.db still carried its pre-install timestamp of 14:28 against an install at 15:53, which is the evidence that the installer did not touch it rather than merely appearing not to.</t>
+        </is>
+      </c>
+      <c r="K69" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pass</t>
+        </is>
+      </c>
+      <c r="L69" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Project owner</t>
+        </is>
+      </c>
+      <c r="M69" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-069</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Deployment</t>
+        </is>
+      </c>
+      <c r="C70" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Re-running the installer upgrades in place and keeps everything</t>
+        </is>
+      </c>
+      <c r="D70" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">REG</t>
+        </is>
+      </c>
+      <c r="E70" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Critical</t>
+        </is>
+      </c>
+      <c r="F70" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A previous version is already installed and in use</t>
+        </is>
+      </c>
+      <c r="G70" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Note the slips, licence and calibration
+2. Run the installer again over the existing installation, without uninstalling first
+3. Start the program
+4. Confirm one entry in Add/Remove Programs, not two
+5. Check the data folder permissions</t>
+        </is>
+      </c>
+      <c r="H70" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N/A</t>
+        </is>
+      </c>
+      <c r="I70" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The installer replaces the program in place, leaves the data folder alone, and produces a single installed entry. Slips, licence and calibration all survive, so an update never costs the operator anything.</t>
+        </is>
+      </c>
+      <c r="J70" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The installer was run a second time over the existing installation and the data survived intact. The fixed AppId means it upgrades rather than installing alongside itself. The data folder carries BUILTIN\\Users:(OI)(CI)(M) on both C:\ProgramData\UitvalSlips and its Backups subfolder, so a standard user retains write access after an installation performed by an administrator -- the failure this grant exists to prevent could only ever have appeared on the customer's machine, never on the developer's.</t>
+        </is>
+      </c>
+      <c r="K70" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pass</t>
+        </is>
+      </c>
+      <c r="L70" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Project owner</t>
+        </is>
+      </c>
+      <c r="M70" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-08-19</t>
         </is>

--- a/docs/Test_Case_Matrix.xlsx
+++ b/docs/Test_Case_Matrix.xlsx
@@ -1361,7 +1361,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:M70"/>
+  <dimension ref="A1:M71"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="9"/>
@@ -5469,6 +5469,78 @@
         </is>
       </c>
       <c r="M70" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-070</t>
+        </is>
+      </c>
+      <c r="B71" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Deployment</t>
+        </is>
+      </c>
+      <c r="C71" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A clean install on a machine holding no data behaves as a new customer's would</t>
+        </is>
+      </c>
+      <c r="D71" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FT</t>
+        </is>
+      </c>
+      <c r="E71" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Critical</t>
+        </is>
+      </c>
+      <c r="F71" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The program is installed but no data folder exists, as on a machine that has never run it</t>
+        </is>
+      </c>
+      <c r="G71" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Close the program and rename C:\ProgramData\UitvalSlips aside
+2. Launch from the installed shortcut
+3. Confirm First-Time Setup appears and complete it
+4. Confirm the licence screen appears
+5. Confirm Slip History and the Main Page are empty
+6. Restore the original folder and confirm everything returns</t>
+        </is>
+      </c>
+      <c r="H71" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N/A</t>
+        </is>
+      </c>
+      <c r="I71" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">First-Time Setup runs, the licence screen follows it, and the program opens with no slips - the sequence a customer meets on a machine that has never run it. Restoring the original data folder returns the installation exactly as it was.</t>
+        </is>
+      </c>
+      <c r="J71" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">First-Time Setup appeared with the seeded defaults rather than any carried-over settings: paper size read Small240x102, not the Small151x151 this machine had been calibrated to, which is the evidence it was genuinely reading fresh rather than finding old state. The setup screen carried the copyright and one-computer-one-site notice, so the terms reach the operator even when someone else ran the installer. The licence screen followed, showing the same machine code as before because the hardware fingerprint is independent of the data folder. Main Page and Slip History both showed nothing at all. After restoring the folder the database was byte-for-byte identical to a copy taken beforehand and licence.lic kept its original timestamp, so the test cost nothing.</t>
+        </is>
+      </c>
+      <c r="K71" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pass</t>
+        </is>
+      </c>
+      <c r="L71" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Project owner</t>
+        </is>
+      </c>
+      <c r="M71" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-08-19</t>
         </is>
